--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -84864,7 +84864,7 @@
         <v>64295.61</v>
       </c>
       <c r="F4222" t="n">
-        <v>2194.33986465</v>
+        <v>2186.14760065</v>
       </c>
     </row>
     <row r="4223">
@@ -84884,7 +84884,7 @@
         <v>65341.07</v>
       </c>
       <c r="F4223" t="n">
-        <v>2403.28829404</v>
+        <v>2395.61925106</v>
       </c>
     </row>
     <row r="4224">
@@ -84915,16 +84915,16 @@
         <v>63693.44</v>
       </c>
       <c r="C4225" t="n">
-        <v>63767.72</v>
+        <v>64041.02</v>
       </c>
       <c r="D4225" t="n">
         <v>62645.39</v>
       </c>
       <c r="E4225" t="n">
-        <v>63096.74</v>
+        <v>63606.36</v>
       </c>
       <c r="F4225" t="n">
-        <v>2844.23476162</v>
+        <v>4486.8368057</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4225"/>
+  <dimension ref="A1:F4226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84724,7 +84724,7 @@
         <v>64796.36</v>
       </c>
       <c r="F4215" t="n">
-        <v>3138.97188353</v>
+        <v>3137.26845193</v>
       </c>
     </row>
     <row r="4216">
@@ -84784,7 +84784,7 @@
         <v>66516.17999999999</v>
       </c>
       <c r="F4218" t="n">
-        <v>7306.01635962</v>
+        <v>7290.45610079</v>
       </c>
     </row>
     <row r="4219">
@@ -84844,7 +84844,7 @@
         <v>64083.32</v>
       </c>
       <c r="F4221" t="n">
-        <v>7395.86448988</v>
+        <v>7355.74034588</v>
       </c>
     </row>
     <row r="4222">
@@ -84904,7 +84904,7 @@
         <v>63694.43</v>
       </c>
       <c r="F4224" t="n">
-        <v>5089.68901464</v>
+        <v>5083.26379546</v>
       </c>
     </row>
     <row r="4225">
@@ -84921,10 +84921,30 @@
         <v>62645.39</v>
       </c>
       <c r="E4225" t="n">
-        <v>63911.64</v>
+        <v>63847.12</v>
       </c>
       <c r="F4225" t="n">
-        <v>5650.70748832</v>
+        <v>6255.44504533</v>
+      </c>
+    </row>
+    <row r="4226">
+      <c r="A4226" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B4226" t="n">
+        <v>63847.12</v>
+      </c>
+      <c r="C4226" t="n">
+        <v>64665.3</v>
+      </c>
+      <c r="D4226" t="n">
+        <v>63500.63</v>
+      </c>
+      <c r="E4226" t="n">
+        <v>64417.5</v>
+      </c>
+      <c r="F4226" t="n">
+        <v>2785.99539415</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4226"/>
+  <dimension ref="A1:F4227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84904,7 +84904,7 @@
         <v>63694.43</v>
       </c>
       <c r="F4224" t="n">
-        <v>5083.26379546</v>
+        <v>5078.62364884</v>
       </c>
     </row>
     <row r="4225">
@@ -84924,7 +84924,7 @@
         <v>63847.12</v>
       </c>
       <c r="F4225" t="n">
-        <v>6255.44504533</v>
+        <v>6244.27561894</v>
       </c>
     </row>
     <row r="4226">
@@ -84941,10 +84941,30 @@
         <v>63194.45</v>
       </c>
       <c r="E4226" t="n">
-        <v>63452.97</v>
+        <v>63896.14</v>
       </c>
       <c r="F4226" t="n">
-        <v>7500.01038926</v>
+        <v>8109.22164518</v>
+      </c>
+    </row>
+    <row r="4227">
+      <c r="A4227" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B4227" t="n">
+        <v>63896.14</v>
+      </c>
+      <c r="C4227" t="n">
+        <v>65118.08</v>
+      </c>
+      <c r="D4227" t="n">
+        <v>63502.91</v>
+      </c>
+      <c r="E4227" t="n">
+        <v>64847.07</v>
+      </c>
+      <c r="F4227" t="n">
+        <v>7804.14299441</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4227"/>
+  <dimension ref="A1:F4228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84904,7 +84904,7 @@
         <v>63694.43</v>
       </c>
       <c r="F4224" t="n">
-        <v>5078.62364884</v>
+        <v>5083.26379546</v>
       </c>
     </row>
     <row r="4225">
@@ -84961,10 +84961,30 @@
         <v>63502.91</v>
       </c>
       <c r="E4227" t="n">
-        <v>64847.07</v>
+        <v>64721.9</v>
       </c>
       <c r="F4227" t="n">
-        <v>7804.14299441</v>
+        <v>8068.47627587</v>
+      </c>
+    </row>
+    <row r="4228">
+      <c r="A4228" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B4228" t="n">
+        <v>64721.9</v>
+      </c>
+      <c r="C4228" t="n">
+        <v>65360</v>
+      </c>
+      <c r="D4228" t="n">
+        <v>62358.96</v>
+      </c>
+      <c r="E4228" t="n">
+        <v>62870.85</v>
+      </c>
+      <c r="F4228" t="n">
+        <v>8023.72897358</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4228"/>
+  <dimension ref="A1:F4231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84904,7 +84904,7 @@
         <v>63694.43</v>
       </c>
       <c r="F4224" t="n">
-        <v>5083.26379546</v>
+        <v>5078.62364884</v>
       </c>
     </row>
     <row r="4225">
@@ -84964,7 +84964,7 @@
         <v>64721.9</v>
       </c>
       <c r="F4227" t="n">
-        <v>8068.47627587</v>
+        <v>8067.167817</v>
       </c>
     </row>
     <row r="4228">
@@ -84981,10 +84981,70 @@
         <v>62358.96</v>
       </c>
       <c r="E4228" t="n">
-        <v>62870.85</v>
+        <v>62825.9</v>
       </c>
       <c r="F4228" t="n">
-        <v>8023.72897358</v>
+        <v>8265.369927080001</v>
+      </c>
+    </row>
+    <row r="4229">
+      <c r="A4229" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B4229" t="n">
+        <v>62826.69</v>
+      </c>
+      <c r="C4229" t="n">
+        <v>63093</v>
+      </c>
+      <c r="D4229" t="n">
+        <v>62209.81</v>
+      </c>
+      <c r="E4229" t="n">
+        <v>62764.2</v>
+      </c>
+      <c r="F4229" t="n">
+        <v>3061.56069477</v>
+      </c>
+    </row>
+    <row r="4230">
+      <c r="A4230" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B4230" t="n">
+        <v>62764.2</v>
+      </c>
+      <c r="C4230" t="n">
+        <v>63730.49</v>
+      </c>
+      <c r="D4230" t="n">
+        <v>62743.87</v>
+      </c>
+      <c r="E4230" t="n">
+        <v>63499.49</v>
+      </c>
+      <c r="F4230" t="n">
+        <v>3307.98726585</v>
+      </c>
+    </row>
+    <row r="4231">
+      <c r="A4231" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B4231" t="n">
+        <v>63499.49</v>
+      </c>
+      <c r="C4231" t="n">
+        <v>64032.43</v>
+      </c>
+      <c r="D4231" t="n">
+        <v>62210.14</v>
+      </c>
+      <c r="E4231" t="n">
+        <v>63461.51</v>
+      </c>
+      <c r="F4231" t="n">
+        <v>6870.88943861</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4234"/>
+  <dimension ref="A1:F4235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85101,10 +85101,30 @@
         <v>64087.41</v>
       </c>
       <c r="E4234" t="n">
-        <v>64280.84</v>
+        <v>64267.3</v>
       </c>
       <c r="F4234" t="n">
-        <v>4464.38307859</v>
+        <v>4534.44439286</v>
+      </c>
+    </row>
+    <row r="4235">
+      <c r="A4235" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B4235" t="n">
+        <v>64267.3</v>
+      </c>
+      <c r="C4235" t="n">
+        <v>64391.35</v>
+      </c>
+      <c r="D4235" t="n">
+        <v>64170.41</v>
+      </c>
+      <c r="E4235" t="n">
+        <v>64336.23</v>
+      </c>
+      <c r="F4235" t="n">
+        <v>103.3990638</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4238"/>
+  <dimension ref="A1:F4239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85044,7 +85044,7 @@
         <v>63466.51</v>
       </c>
       <c r="F4231" t="n">
-        <v>7103.15892039</v>
+        <v>7094.66905383</v>
       </c>
     </row>
     <row r="4232">
@@ -85064,7 +85064,7 @@
         <v>64050.51</v>
       </c>
       <c r="F4232" t="n">
-        <v>6271.40893125</v>
+        <v>6255.85273581</v>
       </c>
     </row>
     <row r="4233">
@@ -85084,7 +85084,7 @@
         <v>64603.03</v>
       </c>
       <c r="F4233" t="n">
-        <v>6952.08267987</v>
+        <v>6935.62424</v>
       </c>
     </row>
     <row r="4234">
@@ -85104,7 +85104,7 @@
         <v>64267.3</v>
       </c>
       <c r="F4234" t="n">
-        <v>4533.94616298</v>
+        <v>4523.48457312</v>
       </c>
     </row>
     <row r="4235">
@@ -85164,7 +85164,7 @@
         <v>64848.69</v>
       </c>
       <c r="F4237" t="n">
-        <v>3044.27393022</v>
+        <v>3044.83384485</v>
       </c>
     </row>
     <row r="4238">
@@ -85181,10 +85181,30 @@
         <v>63733.03</v>
       </c>
       <c r="E4238" t="n">
-        <v>63955.01</v>
+        <v>63911.88</v>
       </c>
       <c r="F4238" t="n">
-        <v>5980.24239242</v>
+        <v>6200.30861168</v>
+      </c>
+    </row>
+    <row r="4239">
+      <c r="A4239" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B4239" t="n">
+        <v>63911.88</v>
+      </c>
+      <c r="C4239" t="n">
+        <v>64439.38</v>
+      </c>
+      <c r="D4239" t="n">
+        <v>63158</v>
+      </c>
+      <c r="E4239" t="n">
+        <v>63654.69</v>
+      </c>
+      <c r="F4239" t="n">
+        <v>5816.55153471</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4239"/>
+  <dimension ref="A1:F4240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85201,10 +85201,30 @@
         <v>63158</v>
       </c>
       <c r="E4239" t="n">
-        <v>63654.69</v>
+        <v>63531.75</v>
       </c>
       <c r="F4239" t="n">
-        <v>5816.55153471</v>
+        <v>6060.72986805</v>
+      </c>
+    </row>
+    <row r="4240">
+      <c r="A4240" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B4240" t="n">
+        <v>63531.75</v>
+      </c>
+      <c r="C4240" t="n">
+        <v>64416.3</v>
+      </c>
+      <c r="D4240" t="n">
+        <v>63235.88</v>
+      </c>
+      <c r="E4240" t="n">
+        <v>63426.81</v>
+      </c>
+      <c r="F4240" t="n">
+        <v>6278.67245767</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4240"/>
+  <dimension ref="A1:F4241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85204,7 +85204,7 @@
         <v>63531.75</v>
       </c>
       <c r="F4239" t="n">
-        <v>6060.72986805</v>
+        <v>6022.83542627</v>
       </c>
     </row>
     <row r="4240">
@@ -85221,10 +85221,30 @@
         <v>63235.88</v>
       </c>
       <c r="E4240" t="n">
-        <v>63426.81</v>
+        <v>63411.72</v>
       </c>
       <c r="F4240" t="n">
-        <v>6278.67245767</v>
+        <v>6581.71684688</v>
+      </c>
+    </row>
+    <row r="4241">
+      <c r="A4241" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B4241" t="n">
+        <v>63411.71</v>
+      </c>
+      <c r="C4241" t="n">
+        <v>63949.9</v>
+      </c>
+      <c r="D4241" t="n">
+        <v>62772.84</v>
+      </c>
+      <c r="E4241" t="n">
+        <v>63575.52</v>
+      </c>
+      <c r="F4241" t="n">
+        <v>4893.63235066</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4246"/>
+  <dimension ref="A1:F4247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85324,7 +85324,7 @@
         <v>64484.18</v>
       </c>
       <c r="F4245" t="n">
-        <v>6094.71846254</v>
+        <v>6072.00631899</v>
       </c>
     </row>
     <row r="4246">
@@ -85341,10 +85341,30 @@
         <v>63979.36</v>
       </c>
       <c r="E4246" t="n">
-        <v>64564.21</v>
+        <v>64681.33</v>
       </c>
       <c r="F4246" t="n">
-        <v>4793.61738275</v>
+        <v>5123.63229799</v>
+      </c>
+    </row>
+    <row r="4247">
+      <c r="A4247" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B4247" t="n">
+        <v>64681.33</v>
+      </c>
+      <c r="C4247" t="n">
+        <v>70022.44</v>
+      </c>
+      <c r="D4247" t="n">
+        <v>64112.04</v>
+      </c>
+      <c r="E4247" t="n">
+        <v>69810.74000000001</v>
+      </c>
+      <c r="F4247" t="n">
+        <v>15414.89058987</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4248"/>
+  <dimension ref="A1:F4249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85164,7 +85164,7 @@
         <v>64848.69</v>
       </c>
       <c r="F4237" t="n">
-        <v>3044.83384485</v>
+        <v>3044.7920444</v>
       </c>
     </row>
     <row r="4238">
@@ -85184,7 +85184,7 @@
         <v>63911.88</v>
       </c>
       <c r="F4238" t="n">
-        <v>6200.30861168</v>
+        <v>6197.25631607</v>
       </c>
     </row>
     <row r="4239">
@@ -85224,7 +85224,7 @@
         <v>63411.72</v>
       </c>
       <c r="F4240" t="n">
-        <v>6578.34665686</v>
+        <v>6570.11779136</v>
       </c>
     </row>
     <row r="4241">
@@ -85284,7 +85284,7 @@
         <v>63018.75</v>
       </c>
       <c r="F4243" t="n">
-        <v>1233.84704082</v>
+        <v>1233.61349427</v>
       </c>
     </row>
     <row r="4244">
@@ -85304,7 +85304,7 @@
         <v>62836.66</v>
       </c>
       <c r="F4244" t="n">
-        <v>1796.15723831</v>
+        <v>1798.33657485</v>
       </c>
     </row>
     <row r="4245">
@@ -85375,16 +85375,36 @@
         <v>69300.00999999999</v>
       </c>
       <c r="C4248" t="n">
-        <v>73079.09</v>
+        <v>73391.42999999999</v>
       </c>
       <c r="D4248" t="n">
         <v>68853.22</v>
       </c>
       <c r="E4248" t="n">
-        <v>72721.19</v>
+        <v>73011.87</v>
       </c>
       <c r="F4248" t="n">
-        <v>15257.77039357</v>
+        <v>16192.93890694</v>
+      </c>
+    </row>
+    <row r="4249">
+      <c r="A4249" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B4249" t="n">
+        <v>73010.86</v>
+      </c>
+      <c r="C4249" t="n">
+        <v>79500</v>
+      </c>
+      <c r="D4249" t="n">
+        <v>73004.7</v>
+      </c>
+      <c r="E4249" t="n">
+        <v>78452.00999999999</v>
+      </c>
+      <c r="F4249" t="n">
+        <v>19316.35875489</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4249"/>
+  <dimension ref="A1:F4252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85401,10 +85401,70 @@
         <v>73004.7</v>
       </c>
       <c r="E4249" t="n">
-        <v>78452.00999999999</v>
+        <v>78325.53999999999</v>
       </c>
       <c r="F4249" t="n">
-        <v>19316.35875489</v>
+        <v>20270.02571641</v>
+      </c>
+    </row>
+    <row r="4250">
+      <c r="A4250" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B4250" t="n">
+        <v>78325.53999999999</v>
+      </c>
+      <c r="C4250" t="n">
+        <v>78828.37</v>
+      </c>
+      <c r="D4250" t="n">
+        <v>76471.7</v>
+      </c>
+      <c r="E4250" t="n">
+        <v>77054.44</v>
+      </c>
+      <c r="F4250" t="n">
+        <v>5408.41850046</v>
+      </c>
+    </row>
+    <row r="4251">
+      <c r="A4251" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B4251" t="n">
+        <v>77054.44</v>
+      </c>
+      <c r="C4251" t="n">
+        <v>78055.25</v>
+      </c>
+      <c r="D4251" t="n">
+        <v>75538.12</v>
+      </c>
+      <c r="E4251" t="n">
+        <v>77729.36</v>
+      </c>
+      <c r="F4251" t="n">
+        <v>4605.87641523</v>
+      </c>
+    </row>
+    <row r="4252">
+      <c r="A4252" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B4252" t="n">
+        <v>77729.36</v>
+      </c>
+      <c r="C4252" t="n">
+        <v>79999.99000000001</v>
+      </c>
+      <c r="D4252" t="n">
+        <v>76652</v>
+      </c>
+      <c r="E4252" t="n">
+        <v>78976.09</v>
+      </c>
+      <c r="F4252" t="n">
+        <v>10888.61266287</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4252"/>
+  <dimension ref="A1:F4253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85424,7 +85424,7 @@
         <v>77054.44</v>
       </c>
       <c r="F4250" t="n">
-        <v>5408.41850046</v>
+        <v>5418.72402749</v>
       </c>
     </row>
     <row r="4251">
@@ -85461,10 +85461,30 @@
         <v>76652</v>
       </c>
       <c r="E4252" t="n">
-        <v>78976.09</v>
+        <v>78981.59</v>
       </c>
       <c r="F4252" t="n">
-        <v>10888.61266287</v>
+        <v>11246.76335657</v>
+      </c>
+    </row>
+    <row r="4253">
+      <c r="A4253" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B4253" t="n">
+        <v>78981.59</v>
+      </c>
+      <c r="C4253" t="n">
+        <v>81265.3</v>
+      </c>
+      <c r="D4253" t="n">
+        <v>77832</v>
+      </c>
+      <c r="E4253" t="n">
+        <v>78592.66</v>
+      </c>
+      <c r="F4253" t="n">
+        <v>10318.55892141</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -85384,7 +85384,7 @@
         <v>73011.87</v>
       </c>
       <c r="F4248" t="n">
-        <v>16192.93890694</v>
+        <v>16177.50127097</v>
       </c>
     </row>
     <row r="4249">
@@ -85444,7 +85444,7 @@
         <v>77729.36</v>
       </c>
       <c r="F4251" t="n">
-        <v>4605.87641523</v>
+        <v>4603.44674424</v>
       </c>
     </row>
     <row r="4252">
@@ -85464,7 +85464,7 @@
         <v>78981.59</v>
       </c>
       <c r="F4252" t="n">
-        <v>11246.76335657</v>
+        <v>11220.09166046</v>
       </c>
     </row>
     <row r="4253">
@@ -85484,7 +85484,7 @@
         <v>78526.8</v>
       </c>
       <c r="F4253" t="n">
-        <v>10841.36239141</v>
+        <v>10823.92193111</v>
       </c>
     </row>
     <row r="4254">
@@ -85538,13 +85538,13 @@
         <v>81479.5</v>
       </c>
       <c r="D4256" t="n">
-        <v>79559.95</v>
+        <v>76845.71000000001</v>
       </c>
       <c r="E4256" t="n">
-        <v>79867.89</v>
+        <v>77369.2</v>
       </c>
       <c r="F4256" t="n">
-        <v>2720.12700243</v>
+        <v>10200.20052428</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4261"/>
+  <dimension ref="A1:F4262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85624,7 +85624,7 @@
         <v>77398.69</v>
       </c>
       <c r="F4260" t="n">
-        <v>7534.76513593</v>
+        <v>7530.85769874</v>
       </c>
     </row>
     <row r="4261">
@@ -85641,10 +85641,30 @@
         <v>76219.17999999999</v>
       </c>
       <c r="E4261" t="n">
-        <v>77023.46000000001</v>
+        <v>77307.36</v>
       </c>
       <c r="F4261" t="n">
-        <v>4766.40315484</v>
+        <v>4999.4595053</v>
+      </c>
+    </row>
+    <row r="4262">
+      <c r="A4262" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B4262" t="n">
+        <v>77307.36</v>
+      </c>
+      <c r="C4262" t="n">
+        <v>82283</v>
+      </c>
+      <c r="D4262" t="n">
+        <v>76929.28999999999</v>
+      </c>
+      <c r="E4262" t="n">
+        <v>81325.21000000001</v>
+      </c>
+      <c r="F4262" t="n">
+        <v>10576.40294754</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4262"/>
+  <dimension ref="A1:F4263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85444,7 +85444,7 @@
         <v>77729.36</v>
       </c>
       <c r="F4251" t="n">
-        <v>4605.87641523</v>
+        <v>4603.44674424</v>
       </c>
     </row>
     <row r="4252">
@@ -85464,7 +85464,7 @@
         <v>78981.59</v>
       </c>
       <c r="F4252" t="n">
-        <v>11246.76335657</v>
+        <v>11220.09166046</v>
       </c>
     </row>
     <row r="4253">
@@ -85484,7 +85484,7 @@
         <v>78526.8</v>
       </c>
       <c r="F4253" t="n">
-        <v>10841.36239141</v>
+        <v>10823.92193111</v>
       </c>
     </row>
     <row r="4254">
@@ -85504,7 +85504,7 @@
         <v>79026.17999999999</v>
       </c>
       <c r="F4254" t="n">
-        <v>6501.6414012</v>
+        <v>6501.40352786</v>
       </c>
     </row>
     <row r="4255">
@@ -85524,7 +85524,7 @@
         <v>80275.34</v>
       </c>
       <c r="F4255" t="n">
-        <v>9668.81938003</v>
+        <v>9601.69454024</v>
       </c>
     </row>
     <row r="4256">
@@ -85544,7 +85544,7 @@
         <v>77839.19</v>
       </c>
       <c r="F4256" t="n">
-        <v>11874.05385306</v>
+        <v>11768.30216671</v>
       </c>
     </row>
     <row r="4257">
@@ -85644,7 +85644,7 @@
         <v>77307.36</v>
       </c>
       <c r="F4261" t="n">
-        <v>4999.4595053</v>
+        <v>4986.73785569</v>
       </c>
     </row>
     <row r="4262">
@@ -85661,10 +85661,30 @@
         <v>76929.28999999999</v>
       </c>
       <c r="E4262" t="n">
-        <v>81325.21000000001</v>
+        <v>81263.99000000001</v>
       </c>
       <c r="F4262" t="n">
-        <v>10576.40294754</v>
+        <v>11057.12108519</v>
+      </c>
+    </row>
+    <row r="4263">
+      <c r="A4263" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B4263" t="n">
+        <v>81263.99000000001</v>
+      </c>
+      <c r="C4263" t="n">
+        <v>81438.00999999999</v>
+      </c>
+      <c r="D4263" t="n">
+        <v>78626</v>
+      </c>
+      <c r="E4263" t="n">
+        <v>79728.42999999999</v>
+      </c>
+      <c r="F4263" t="n">
+        <v>6573.11412021</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4263"/>
+  <dimension ref="A1:F4266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85624,7 +85624,7 @@
         <v>77398.69</v>
       </c>
       <c r="F4260" t="n">
-        <v>7530.85769874</v>
+        <v>7524.0890438</v>
       </c>
     </row>
     <row r="4261">
@@ -85664,7 +85664,7 @@
         <v>81263.99000000001</v>
       </c>
       <c r="F4262" t="n">
-        <v>11057.12108519</v>
+        <v>11051.6272806</v>
       </c>
     </row>
     <row r="4263">
@@ -85681,10 +85681,70 @@
         <v>78626</v>
       </c>
       <c r="E4263" t="n">
-        <v>79728.42999999999</v>
+        <v>79675.12</v>
       </c>
       <c r="F4263" t="n">
-        <v>6573.11412021</v>
+        <v>6701.30488302</v>
+      </c>
+    </row>
+    <row r="4264">
+      <c r="A4264" s="1" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B4264" t="n">
+        <v>79675.12</v>
+      </c>
+      <c r="C4264" t="n">
+        <v>80200.67</v>
+      </c>
+      <c r="D4264" t="n">
+        <v>79458.74000000001</v>
+      </c>
+      <c r="E4264" t="n">
+        <v>79831.57000000001</v>
+      </c>
+      <c r="F4264" t="n">
+        <v>2148.24687031</v>
+      </c>
+    </row>
+    <row r="4265">
+      <c r="A4265" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B4265" t="n">
+        <v>79833.86</v>
+      </c>
+      <c r="C4265" t="n">
+        <v>80564.24000000001</v>
+      </c>
+      <c r="D4265" t="n">
+        <v>79250</v>
+      </c>
+      <c r="E4265" t="n">
+        <v>80339.13</v>
+      </c>
+      <c r="F4265" t="n">
+        <v>2003.19629692</v>
+      </c>
+    </row>
+    <row r="4266">
+      <c r="A4266" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B4266" t="n">
+        <v>80339.13</v>
+      </c>
+      <c r="C4266" t="n">
+        <v>80462.23</v>
+      </c>
+      <c r="D4266" t="n">
+        <v>78666</v>
+      </c>
+      <c r="E4266" t="n">
+        <v>79099.86</v>
+      </c>
+      <c r="F4266" t="n">
+        <v>3101.12178078</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4266"/>
+  <dimension ref="A1:F4267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85624,7 +85624,7 @@
         <v>77398.69</v>
       </c>
       <c r="F4260" t="n">
-        <v>7524.0890438</v>
+        <v>7530.85769874</v>
       </c>
     </row>
     <row r="4261">
@@ -85741,10 +85741,30 @@
         <v>78666</v>
       </c>
       <c r="E4266" t="n">
-        <v>79099.86</v>
+        <v>79091.97</v>
       </c>
       <c r="F4266" t="n">
-        <v>3101.12178078</v>
+        <v>3307.92577702</v>
+      </c>
+    </row>
+    <row r="4267">
+      <c r="A4267" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B4267" t="n">
+        <v>79091.97</v>
+      </c>
+      <c r="C4267" t="n">
+        <v>79477.07000000001</v>
+      </c>
+      <c r="D4267" t="n">
+        <v>77589</v>
+      </c>
+      <c r="E4267" t="n">
+        <v>78536.28999999999</v>
+      </c>
+      <c r="F4267" t="n">
+        <v>5020.57316802</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4267"/>
+  <dimension ref="A1:F4268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85624,7 +85624,7 @@
         <v>77398.69</v>
       </c>
       <c r="F4260" t="n">
-        <v>7530.85769874</v>
+        <v>7524.0890438</v>
       </c>
     </row>
     <row r="4261">
@@ -85744,7 +85744,7 @@
         <v>79091.97</v>
       </c>
       <c r="F4266" t="n">
-        <v>3307.92577702</v>
+        <v>3298.65347113</v>
       </c>
     </row>
     <row r="4267">
@@ -85761,10 +85761,30 @@
         <v>77589</v>
       </c>
       <c r="E4267" t="n">
-        <v>78536.28999999999</v>
+        <v>78447.11</v>
       </c>
       <c r="F4267" t="n">
-        <v>5020.57316802</v>
+        <v>5167.76242688</v>
+      </c>
+    </row>
+    <row r="4268">
+      <c r="A4268" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B4268" t="n">
+        <v>78449.28</v>
+      </c>
+      <c r="C4268" t="n">
+        <v>79752.73</v>
+      </c>
+      <c r="D4268" t="n">
+        <v>77727</v>
+      </c>
+      <c r="E4268" t="n">
+        <v>77986.7</v>
+      </c>
+      <c r="F4268" t="n">
+        <v>5107.31930182</v>
       </c>
     </row>
   </sheetData>
